--- a/forms/trg/Formulir_TRG_mwm-rg.xlsx
+++ b/forms/trg/Formulir_TRG_mwm-rg.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B25)</f>
+        <f>COUNTA(Anggota!B5:B26)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F25)</f>
+        <f>COUNTA(Anggota!F5:F26)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,22 +913,22 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. dr. Prihantono, Sp.B. Subsp.Onk(K)</t>
+          <t>Dr. Takdir Tahir, S.Kep., Ns., M.Kes.</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Leader</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
-          <t>Breast Conserving Surgery, Oncology Diagnostic, Radical Modify Mastectomy</t>
+          <t>Department of Medical Surgical Nursing, Faculty of Nursing, Hasanuddin University</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Department of Oncology, Faculty of Medicine, Hasanuddin University</t>
+          <t>Malignant Wound Management, Wound Healing and Theraphy, Diabetic Foot Ulcres, Medical Surgical Nursing</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
@@ -937,17 +937,17 @@
       <c r="I5" s="12" t="n"/>
       <c r="J5" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-8247-0457</t>
+          <t>0000-0001-9356-1242</t>
         </is>
       </c>
       <c r="K5" s="11" t="inlineStr">
         <is>
-          <t>5975889</t>
+          <t>6039190</t>
         </is>
       </c>
       <c r="L5" s="11" t="inlineStr">
         <is>
-          <t>57194563605</t>
+          <t>57193349327</t>
         </is>
       </c>
       <c r="M5" s="11" t="inlineStr">
@@ -962,22 +962,22 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Ns. Ummi Pratiwi S.Kep., MSN., Ph.D</t>
+          <t>Prof. Dr. dr. Prihantono, Sp.B. Subsp.Onk(K)</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>Oncology and Palliative Care</t>
+          <t>Breast Conserving Surgery, Oncology Diagnostic, Radical Modify Mastectomy</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Department of Medical Surgical Nursing, Faculty of Nursing, Hasanuddin University</t>
+          <t>Department of Oncology, Faculty of Medicine, Hasanuddin University</t>
         </is>
       </c>
       <c r="F6" s="12" t="n"/>
@@ -986,15 +986,19 @@
       <c r="I6" s="12" t="n"/>
       <c r="J6" s="11" t="inlineStr">
         <is>
-          <t>0009-0005-9851-7095</t>
+          <t>0000-0002-8247-0457</t>
         </is>
       </c>
       <c r="K6" s="11" t="inlineStr">
         <is>
-          <t>6942473</t>
-        </is>
-      </c>
-      <c r="L6" s="12" t="n"/>
+          <t>5975889</t>
+        </is>
+      </c>
+      <c r="L6" s="11" t="inlineStr">
+        <is>
+          <t>57194563605</t>
+        </is>
+      </c>
       <c r="M6" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1007,22 +1011,22 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Dr. Andi Rizky Arbaim Hasyar, S.Ft, Physio</t>
+          <t>Ns. Ummi Pratiwi S.Kep., MSN., Ph.D</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>Cardiovascular and Respiratory Physiotherapy</t>
+          <t>Oncology and Palliative Care</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Department of Physiotherapy, Faculty of Nursing, Hasanuddin University</t>
+          <t>Department of Medical Surgical Nursing, Faculty of Nursing, Hasanuddin University</t>
         </is>
       </c>
       <c r="F7" s="12" t="n"/>
@@ -1031,19 +1035,15 @@
       <c r="I7" s="12" t="n"/>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t>0000-0003-2230-8754</t>
+          <t>0009-0005-9851-7095</t>
         </is>
       </c>
       <c r="K7" s="11" t="inlineStr">
         <is>
-          <t>6801912</t>
-        </is>
-      </c>
-      <c r="L7" s="11" t="inlineStr">
-        <is>
-          <t>57226736941</t>
-        </is>
-      </c>
+          <t>6942473</t>
+        </is>
+      </c>
+      <c r="L7" s="12" t="n"/>
       <c r="M7" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1056,22 +1056,22 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Lai Lee Lee., Ph.D</t>
+          <t>Dr. Andi Rizky Arbaim Hasyar, S.Ft, Physio</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>Clinical Breast Surgical Oncology, Oncoplastic Breast Surgery &amp; Reconstruction, Breast Cancer Epidemiology</t>
+          <t>Cardiovascular and Respiratory Physiotherapy</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>Faculty of Medicine, Malaya University, Malaysia</t>
+          <t>Department of Physiotherapy, Faculty of Nursing, Hasanuddin University</t>
         </is>
       </c>
       <c r="F8" s="12" t="n"/>
@@ -1080,13 +1080,17 @@
       <c r="I8" s="12" t="n"/>
       <c r="J8" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-0783-6340</t>
-        </is>
-      </c>
-      <c r="K8" s="12" t="n"/>
+          <t>0000-0003-2230-8754</t>
+        </is>
+      </c>
+      <c r="K8" s="11" t="inlineStr">
+        <is>
+          <t>6801912</t>
+        </is>
+      </c>
       <c r="L8" s="11" t="inlineStr">
         <is>
-          <t>56825043600</t>
+          <t>57226736941</t>
         </is>
       </c>
       <c r="M8" s="11" t="inlineStr">
@@ -1101,31 +1105,39 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Fahad Alanezi, PhD, MSc, RN</t>
+          <t>Lai Lee Lee., Ph.D</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>Wound Care, Cardiovascular</t>
+          <t>Clinical Breast Surgical Oncology, Oncoplastic Breast Surgery &amp; Reconstruction, Breast Cancer Epidemiology</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Dr. Sulaiman Al Habib College</t>
+          <t>Faculty of Medicine, Malaya University, Malaysia</t>
         </is>
       </c>
       <c r="F9" s="12" t="n"/>
       <c r="G9" s="12" t="n"/>
       <c r="H9" s="12" t="n"/>
       <c r="I9" s="12" t="n"/>
-      <c r="J9" s="12" t="n"/>
+      <c r="J9" s="11" t="inlineStr">
+        <is>
+          <t>0000-0002-0783-6340</t>
+        </is>
+      </c>
       <c r="K9" s="12" t="n"/>
-      <c r="L9" s="12" t="n"/>
+      <c r="L9" s="11" t="inlineStr">
+        <is>
+          <t>56825043600</t>
+        </is>
+      </c>
       <c r="M9" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1138,22 +1150,22 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Ns. Lisna. S.Kep.,M.Kep., Sp.,Kep., Onk, CBOnN</t>
+          <t>Fahad Alanezi, PhD, MSc, RN</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>Oncology Nursing Specialist : Breast Cancer Specialist</t>
+          <t>Wound Care, Cardiovascular</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>Wahidin Sudirohusodo Hospital, Makassar</t>
+          <t>Dr. Sulaiman Al Habib College</t>
         </is>
       </c>
       <c r="F10" s="12" t="n"/>
@@ -1175,18 +1187,22 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Ns. Fifi Riskayanti S.Kep.,</t>
+          <t>Ns. Lisna. S.Kep.,M.Kep., Sp.,Kep., Onk, CBOnN</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="n"/>
+          <t>Researcher</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>Oncology Nursing Specialist : Breast Cancer Specialist</t>
+        </is>
+      </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>Dharmais Cancer Hospital, National Cancer Center, Indonesia</t>
+          <t>Wahidin Sudirohusodo Hospital, Makassar</t>
         </is>
       </c>
       <c r="F11" s="12" t="n"/>
@@ -1208,20 +1224,20 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Meivie Cindy Maulany</t>
+          <t>Ns. Fifi Riskayanti S.Kep.,</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
-        </is>
-      </c>
-      <c r="D12" s="11" t="inlineStr">
-        <is>
-          <t>Faculty of Nursing Hasanuddin University</t>
-        </is>
-      </c>
-      <c r="E12" s="11" t="n"/>
+          <t>Researcher</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="n"/>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>Dharmais Cancer Hospital, National Cancer Center, Indonesia</t>
+        </is>
+      </c>
       <c r="F12" s="12" t="n"/>
       <c r="G12" s="12" t="n"/>
       <c r="H12" s="12" t="n"/>
@@ -1241,12 +1257,12 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Kuliahna.K</t>
+          <t>Meivie Cindy Maulany</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
@@ -1254,11 +1270,7 @@
           <t>Faculty of Nursing Hasanuddin University</t>
         </is>
       </c>
-      <c r="E13" s="11" t="inlineStr">
-        <is>
-          <t>Cancer remains a major global health issue, with the prevalence of cancer cases continuing to rise every year in both developed and developing countries. According to the Global Cancer Observatory, which reports estimates of the cancer burden in 185 countries worldwide, the five most common types of cancer globally, in order, are: lung cancer, breast cancer, colorectal cancer, prostate cancer, and stomach cancer.</t>
-        </is>
-      </c>
+      <c r="E13" s="11" t="n"/>
       <c r="F13" s="12" t="n"/>
       <c r="G13" s="12" t="n"/>
       <c r="H13" s="12" t="n"/>
@@ -1276,10 +1288,26 @@
       <c r="A14" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="12" t="n"/>
-      <c r="C14" s="12" t="n"/>
-      <c r="D14" s="12" t="n"/>
-      <c r="E14" s="11" t="n"/>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>Kuliahna.K</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t>Faculty of Nursing Hasanuddin University</t>
+        </is>
+      </c>
+      <c r="E14" s="11" t="inlineStr">
+        <is>
+          <t>Cancer remains a major global health issue, with the prevalence of cancer cases continuing to rise every year in both developed and developing countries. According to the Global Cancer Observatory, which reports estimates of the cancer burden in 185 countries worldwide, the five most common types of cancer globally, in order, are: lung cancer, breast cancer, colorectal cancer, prostate cancer, and stomach cancer.</t>
+        </is>
+      </c>
       <c r="F14" s="12" t="n"/>
       <c r="G14" s="12" t="n"/>
       <c r="H14" s="12" t="n"/>
@@ -1287,7 +1315,11 @@
       <c r="J14" s="12" t="n"/>
       <c r="K14" s="12" t="n"/>
       <c r="L14" s="12" t="n"/>
-      <c r="M14" s="12" t="n"/>
+      <c r="M14" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
@@ -1476,15 +1508,32 @@
       <c r="L25" s="12" t="n"/>
       <c r="M25" s="12" t="n"/>
     </row>
+    <row r="26">
+      <c r="A26" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="12" t="n"/>
+      <c r="C26" s="12" t="n"/>
+      <c r="D26" s="12" t="n"/>
+      <c r="E26" s="11" t="n"/>
+      <c r="F26" s="12" t="n"/>
+      <c r="G26" s="12" t="n"/>
+      <c r="H26" s="12" t="n"/>
+      <c r="I26" s="12" t="n"/>
+      <c r="J26" s="12" t="n"/>
+      <c r="K26" s="12" t="n"/>
+      <c r="L26" s="12" t="n"/>
+      <c r="M26" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
